--- a/data/trans_camb/IP1015-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,3</t>
+          <t>-1,76; 0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,23</t>
+          <t>-1,91; 0,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,18</t>
+          <t>-0,82; 0,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 0,14</t>
+          <t>-0,86; 0,15</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,09</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,48; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,28</t>
+          <t>-0,57; 0,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,3</t>
+          <t>-0,22; 0,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,14</t>
+          <t>-0,3; 0,13</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,04; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Edad-trans_camb.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,0; 0,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,56</t>
+          <t>-1,65; 0,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,22</t>
+          <t>-1,67; 0,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,15</t>
+          <t>-0,95; 0,18</t>
         </is>
       </c>
     </row>
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,41</t>
+          <t>-0,5; 0,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,27</t>
+          <t>-0,59; 0,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,27</t>
+          <t>-0,23; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,13</t>
+          <t>-0,3; 0,14</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,33</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,75</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,57</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,65; 0,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,93; 0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,3</t>
+          <t>-0,82; 0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,18</t>
+          <t>-0,94; 0,14</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-65,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-69,38%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-65,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-69,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>inf%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>inf%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-0,48; 0,39</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-0,57; 0,28</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,36</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,25</t>
+          <t>-0,21; 0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,92%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-36,2%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-4,92%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-36,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,04; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
